--- a/00 Raw data/SDG/Publications_by_SDG_-_National_Yunlin_University_of_Science_and_Technology.xlsx
+++ b/00 Raw data/SDG/Publications_by_SDG_-_National_Yunlin_University_of_Science_and_Technology.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2018 to 2025</t>
+          <t>2017 to 2025</t>
         </is>
       </c>
     </row>
@@ -157,7 +157,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8 July 2026</t>
+          <t>5 August 2026</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
     </row>
@@ -209,13 +209,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C13" t="n">
-        <v>4.97</v>
+        <v>4.21</v>
       </c>
       <c r="D13" t="n">
-        <v>876.0</v>
+        <v>892.0</v>
       </c>
     </row>
     <row r="14">
@@ -225,13 +225,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.69</v>
+        <v>13.05</v>
       </c>
       <c r="D14" t="n">
-        <v>4055.0</v>
+        <v>4209.0</v>
       </c>
     </row>
     <row r="15">
@@ -241,13 +241,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>491.0</v>
+        <v>502.0</v>
       </c>
       <c r="C15" t="n">
-        <v>9.74</v>
+        <v>9.63</v>
       </c>
       <c r="D15" t="n">
-        <v>39678.0</v>
+        <v>41138.0</v>
       </c>
     </row>
     <row r="16">
@@ -257,13 +257,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>307.0</v>
+        <v>328.0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="D16" t="n">
-        <v>7577.0</v>
+        <v>7999.0</v>
       </c>
     </row>
     <row r="17">
@@ -276,10 +276,10 @@
         <v>20.0</v>
       </c>
       <c r="C17" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="D17" t="n">
-        <v>789.0</v>
+        <v>810.0</v>
       </c>
     </row>
     <row r="18">
@@ -289,13 +289,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>139.0</v>
+        <v>145.0</v>
       </c>
       <c r="C18" t="n">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="D18" t="n">
-        <v>5446.0</v>
+        <v>5688.0</v>
       </c>
     </row>
     <row r="19">
@@ -305,13 +305,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>740.0</v>
+        <v>780.0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="D19" t="n">
-        <v>15785.0</v>
+        <v>16864.0</v>
       </c>
     </row>
     <row r="20">
@@ -321,13 +321,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>167.0</v>
+        <v>175.0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="D20" t="n">
-        <v>4547.0</v>
+        <v>4709.0</v>
       </c>
     </row>
     <row r="21">
@@ -337,13 +337,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>505.0</v>
+        <v>546.0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="D21" t="n">
-        <v>9317.0</v>
+        <v>10018.0</v>
       </c>
     </row>
     <row r="22">
@@ -353,13 +353,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="C22" t="n">
-        <v>9.22</v>
+        <v>8.89</v>
       </c>
       <c r="D22" t="n">
-        <v>3195.0</v>
+        <v>3370.0</v>
       </c>
     </row>
     <row r="23">
@@ -369,13 +369,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>244.0</v>
+        <v>258.0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="D23" t="n">
-        <v>5507.0</v>
+        <v>5742.0</v>
       </c>
     </row>
     <row r="24">
@@ -385,13 +385,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>217.0</v>
+        <v>223.0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="D24" t="n">
-        <v>6369.0</v>
+        <v>6549.0</v>
       </c>
     </row>
     <row r="25">
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>121.0</v>
+        <v>124.0</v>
       </c>
       <c r="C25" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="D25" t="n">
-        <v>3995.0</v>
+        <v>4191.0</v>
       </c>
     </row>
     <row r="26">
@@ -420,10 +420,10 @@
         <v>21.0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="D26" t="n">
-        <v>237.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="27">
@@ -433,13 +433,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
       <c r="C27" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="D27" t="n">
-        <v>1422.0</v>
+        <v>1496.0</v>
       </c>
     </row>
     <row r="28">
@@ -452,10 +452,10 @@
         <v>28.0</v>
       </c>
       <c r="C28" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="D28" t="n">
-        <v>807.0</v>
+        <v>826.0</v>
       </c>
     </row>
     <row r="29">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2328.0</v>
+        <v>2463.0</v>
       </c>
       <c r="C29" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="D29" t="n">
-        <v>77308.0</v>
+        <v>81267.0</v>
       </c>
     </row>
     <row r="30">
